--- a/docs/StructureDefinition-ConsentWithLimits.xlsx
+++ b/docs/StructureDefinition-ConsentWithLimits.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-16T14:50:06-05:00</t>
+    <t>2026-10-14T10:52:49-05:00</t>
   </si>
   <si>
     <t>Publisher</t>
